--- a/output/pdf_financials_xlsx/RYO.xlsx
+++ b/output/pdf_financials_xlsx/RYO.xlsx
@@ -7875,7 +7875,7 @@
         <v>0</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>2.344041</v>
       </c>
     </row>
     <row r="119">
@@ -20731,7 +20731,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RYO.xlsx
+++ b/output/pdf_financials_xlsx/RYO.xlsx
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.116442</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.02885</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.189601</v>
+        <v>-4.306043</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.259898</v>
+        <v>-0.288748</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.153673</v>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.189601</v>
+        <v>-4.306043</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.259898</v>
+        <v>-0.288748</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.153673</v>
@@ -2630,37 +2630,37 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.010087</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.011404</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002961</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003802</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.002766</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.015504</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.042662</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.011917</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.048338</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.015879</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.136266</v>
       </c>
     </row>
     <row r="35">
@@ -2750,37 +2750,37 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.010087</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.011404</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002961</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003802</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.002766</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.015504</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.042662</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.011917</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.048338</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.015879</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.136266</v>
       </c>
     </row>
     <row r="37">
@@ -3470,37 +3470,37 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.047903</v>
+        <v>0.037816</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.015354</v>
+        <v>0.00395</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.009367</v>
+        <v>0.006406</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.009594</v>
+        <v>0.005792</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.03292</v>
+        <v>0.017416</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.0473</v>
+        <v>0.004638</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.037237</v>
+        <v>0.02532</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.07259</v>
+        <v>0.024252</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.688644</v>
+        <v>0.552378</v>
       </c>
     </row>
     <row r="49">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -42199,7 +42199,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -44494,7 +44494,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -52346,7 +52346,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E435" s="5" t="n">

--- a/output/pdf_financials_xlsx/RYO.xlsx
+++ b/output/pdf_financials_xlsx/RYO.xlsx
@@ -7968,7 +7968,7 @@
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>1.089426</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -30534,7 +30534,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
